--- a/site/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Okta-Integration/headings.xlsx
+++ b/site/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Okta-Integration/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,160 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01K2F6ANZ30WMRWZ3HS0H8MAZN</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Okta-Integration/#h_01K2F6ANZ30WMRWZ3HS0H8MAZN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Watchdog Setup</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01K4Q5Q7MJ7FEQ698CCEKVYVD8</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Okta-Integration/#h_01K4Q5Q7MJ7FEQ698CCEKVYVD8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Create Integration Watchdog</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01K4Q5Q7MKCGADBKQRW7EFMD4T</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Okta-Integration/#h_01K4Q5Q7MKCGADBKQRW7EFMD4T</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Okta-Integration/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Okta-Integration/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Okta-Integration/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Okta-Integration/#h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Okta-Integration/headings.xlsx
+++ b/site/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Okta-Integration/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,6 +614,28 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Watchdog Insights</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KQ9AKSTAGRHHECR0BZP7CA26</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Okta-Integration/#h_01KQ9AKSTAGRHHECR0BZP7CA26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
